--- a/textbook_examples/mod03_q03_power_query_answer.xlsx
+++ b/textbook_examples/mod03_q03_power_query_answer.xlsx
@@ -1577,9 +1577,9 @@
       <c r="A6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="e">
-        <f>SUM(#REF!)</f>
-        <v>#REF!</v>
+      <c r="B6" s="8">
+        <f>SUM(q03_tickets[weight_tonnes])</f>
+        <v>614.5</v>
       </c>
     </row>
     <row r="7" spans="1:2">
